--- a/Phytium_PPE_System_SourceCode/05_高阶风险管理6-17.xlsx
+++ b/Phytium_PPE_System_SourceCode/05_高阶风险管理6-17.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>系统在主核系统崩溃、自检失故或 AI 推理死机等异常情况发生时，从核立刻接管硬件外设，保持“蜂鸣器长鸣”皅安全警示状态。</t>
+          <t>系统在主核系统崩溃、自检失故或 AI 推理死机等异常情况发生时，从核立刻接管硬件外设，保持安全警示状态。</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CPU采用AMP软件架构，主从核程序独立运行。主控程序增加心跳模块，定期向从核发送信号。从核监控不到主控程序心跳时，及时发出硬件中断，触发看门狗重启并强制蜂鸣器长鸣报警。</t>
+          <t>CPU采用AMP软件架构，主从核程序独立运行。主控程序增加心跳模块，定期向从核发送信号。从核监控不到主控程序心跳时，及时发出硬件中断，触发看门狗重启并安全制动。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>气体传感器老化失故或ADC采样异常</t>
+          <t>气体传感器老化失故或数字信号采样异常</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>向ADC引脚注入枅限电压模拟传感器硬件击穿故障，测试程序是否能及时发现读数异常并切断继电器保护电路。</t>
+          <t>向GPIO引脚注入枅限电压模拟传感器硬件击穿故障，测试程序是否能及时发现读数异常并切断继电器保护电路。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
